--- a/backend/Plantilla_Carga_Equipos.xlsx
+++ b/backend/Plantilla_Carga_Equipos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Claud\Downloads\project-bolt-sb1-qnazhgui\project\Administracio_gestion_precios_nuevo\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B707FF-9EB4-40EF-9AFF-8AE00AF863A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E204F12-2C23-47D9-9A5F-7735434503DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1605" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>peso_kg</t>
   </si>
@@ -53,13 +53,16 @@
   </si>
   <si>
     <t>Modelo</t>
+  </si>
+  <si>
+    <t>producto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,60 +92,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <name val="Myriad Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Muli"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Muli"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Myriad Pro"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -165,26 +124,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -193,36 +139,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -531,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="33.88671875" style="1" customWidth="1"/>
@@ -587,32 +503,35 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="4"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -634,31 +553,43 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="5"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/Plantilla_Carga_Equipos.xlsx
+++ b/backend/Plantilla_Carga_Equipos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Claud\Downloads\project-bolt-sb1-qnazhgui\project\Administracio_gestion_precios_nuevo\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E204F12-2C23-47D9-9A5F-7735434503DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A251F0F-4B1F-4DAF-A399-9BF674BECBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
     <t>equipo u opcional</t>
   </si>
   <si>
-    <t>fecha cotizacion</t>
-  </si>
-  <si>
     <t>largo_mm</t>
   </si>
   <si>
@@ -56,13 +53,16 @@
   </si>
   <si>
     <t>producto</t>
+  </si>
+  <si>
+    <t>fecha_cotizacion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,7 +448,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="24.77734375" style="1" customWidth="1"/>
@@ -486,7 +486,7 @@
     <col min="35" max="35" width="21.21875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="28.8">
+    <row r="1" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -497,34 +497,34 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -552,7 +552,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -565,7 +565,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -578,7 +578,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
